--- a/24-06-26/Furqan.xlsx
+++ b/24-06-26/Furqan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E57202-E239-42B8-A8F0-2994AAD9B3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AF18C6-D8BE-482B-97AF-87BD42AFDDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="117">
   <si>
     <t>Gm</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>Address: Devis Road</t>
+  </si>
+  <si>
+    <t>no cash</t>
   </si>
 </sst>
 </file>
@@ -3366,7 +3369,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3394,7 +3397,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4587,7 +4590,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4615,7 +4618,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5808,7 +5811,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5836,7 +5839,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7029,7 +7032,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7057,7 +7060,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8250,7 +8253,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8278,7 +8281,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9471,7 +9474,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9499,7 +9502,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10689,7 +10692,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10717,7 +10720,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11906,7 +11909,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11934,7 +11937,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13123,7 +13126,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13151,7 +13154,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14340,7 +14343,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14368,7 +14371,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18307,7 +18310,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18335,7 +18338,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19524,7 +19527,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19552,7 +19555,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20741,7 +20744,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20769,7 +20772,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21958,7 +21961,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -21986,7 +21989,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23180,7 +23183,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23208,7 +23211,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23620,7 +23623,7 @@
       </c>
       <c r="U17" s="164">
         <f>+'4'!P35</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
@@ -23933,11 +23936,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22</f>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>2353.8000000000002</v>
+        <v>784.60000000000014</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -23945,27 +23948,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>82.38300000000001</v>
+        <v>27.461000000000006</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>117.69000000000003</v>
+        <v>39.230000000000011</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>2153.7270000000003</v>
+        <v>717.90900000000011</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>445.10358000000008</v>
+        <v>129.22362000000001</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>64.970764500000001</v>
+        <v>21.178315500000004</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>2663.8013445000001</v>
+        <v>868.31093550000014</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24123,7 +24126,7 @@
       <c r="B25" s="226"/>
       <c r="C25" s="227">
         <f>H25/40</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="221"/>
       <c r="E25" s="221"/>
@@ -24134,11 +24137,11 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>27616.449999999997</v>
+        <v>26047.249999999996</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
@@ -24146,27 +24149,27 @@
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>82.38300000000001</v>
+        <v>27.461000000000006</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>2138.7020000000002</v>
+        <v>2060.2420000000002</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>25395.364999999998</v>
+        <v>23959.546999999999</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>5836.1530900000007</v>
+        <v>5520.2731300000005</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>279.48739905000002</v>
+        <v>235.69495004999999</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>31511.005489050003</v>
+        <v>29715.515080050005</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24296,7 +24299,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>31511.005489050003</v>
+        <v>29715.515080050001</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24329,7 +24332,7 @@
       <c r="O32" s="238"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>27616.449999999997</v>
+        <v>26047.249999999996</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24350,7 +24353,7 @@
       <c r="O33" s="240"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>2138.7020000000002</v>
+        <v>2060.2420000000002</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24371,7 +24374,7 @@
       <c r="O34" s="240"/>
       <c r="P34" s="154">
         <f>K25</f>
-        <v>82.38300000000001</v>
+        <v>27.461000000000006</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24393,7 +24396,7 @@
       <c r="O35" s="240"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>25395.364999999994</v>
+        <v>23959.546999999995</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24418,7 +24421,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>5836.1530900000007</v>
+        <v>5520.2731300000005</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24440,7 +24443,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>31231.518089999994</v>
+        <v>29479.820129999996</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24465,7 +24468,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>780.78795224999988</v>
+        <v>736.99550324999996</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24475,7 +24478,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>32012.306042249995</v>
+        <v>30216.815633249997</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24647,7 +24650,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24675,7 +24678,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25870,7 +25873,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25898,7 +25901,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27103,7 +27106,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27131,7 +27134,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28277,7 +28280,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:XFD37"/>
+  <dimension ref="A1:XFD37"/>
   <sheetFormatPr defaultColWidth="29.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" customWidth="1"/>
@@ -28298,6 +28301,11 @@
     <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
+      <c r="K1" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="199" t="s">
         <v>45</v>
@@ -28347,7 +28355,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28375,7 +28383,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29013,37 +29021,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" hidden="1" x14ac:dyDescent="0.35">
@@ -29173,36 +29179,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -29252,7 +29258,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29273,7 +29279,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29294,7 +29300,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29316,7 +29322,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29341,7 +29347,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29363,7 +29369,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29388,7 +29394,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29398,7 +29404,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29570,7 +29576,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29598,7 +29604,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30791,7 +30797,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30819,7 +30825,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
